--- a/extenbooks/XS1704.xlsx
+++ b/extenbooks/XS1704.xlsx
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1201,165 +1201,174 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Total value (TV) is the classical economic concept of value produced in the productive and trading sectors: TV = c + v + s (constant capital plus variable capital plus surplus-value). It excludes unproductive activities such as finance, government administration, police, courts, defence, and royalty flows (ground rent, interest, patents, taxes). TV is derived by mapping NZSNA data to classical categories for 25 NZ production groups, following Shaikh-Tonak (1994). TV is systematically lower than neoclassical gross output because unproductive sectors are excluded, and lower than GDP for different reasons (GDP = v + s, while TV includes intermediate consumption of productive industries).</t>
+          <t>T7/T1 STUDY ANCHOR (WP-E review, 2026-07-01). XS1704-A digitizes the 'Total value' column of Cronin (2001) Table 1, 'NZSNA in classical categories ($m)': 1972 = 10,423, 1984 = 57,628, 1989 = 96,845, 1995 = 123,284 (millions NZD, current prices). The source CSV matches Cronin Table 1 with 0/24 mismatches; corroborated against the independent HDARP tables.csv. Units already consistent (no decimal/percent issue as with the Table 2 ratio series). This external anchor (the study's own printed Table 1) backs validation.reference_values.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Mapping Total Value); SUMMARY.md</t>
+          <t>Cronin 2001, Table 1 (Total value column; RoPE 13(3):309-327, KB extraction p.11)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series XS1704-A: Digitized from Cronin (2001) Table 1, column 'Total value', 1972-1995 (24 observations). Original table title: 'NZSNA in classical categories ($m)', Review of Political Economy 13(3), p. 11 (Table 1). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Units: millions NZD, current prices.</t>
+          <t>Total value (TV) is the classical economic concept of value produced in the productive and trading sectors: TV = c + v + s (constant capital plus variable capital plus surplus-value). It excludes unproductive activities such as finance, government administration, police, courts, defence, and royalty flows (ground rent, interest, patents, taxes). TV is derived by mapping NZSNA data to classical categories for 25 NZ production groups, following Shaikh-Tonak (1994). TV is systematically lower than neoclassical gross output because unproductive sectors are excluded, and lower than GDP for different reasons (GDP = v + s, while TV includes intermediate consumption of productive industries).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; tables.csv rows 2-26</t>
+          <t>Cronin_2001, body_text.md Section 3 (Mapping Total Value); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Annual total value (millions NZD, current prices): 1972=10423, 1973=12267, 1974=14233, 1975=15553, 1976=18847, 1977=23454, 1978=25195, 1979=28131, 1980=33317, 1981=38400, 1982=46691, 1983=52322, 1984=57628, 1985=67193, 1986=77232, 1987=87537, 1988=93389, 1989=96845, 1990=100038, 1991=100112, 1992=100125, 1993=105252, 1994=115853, 1995=123284.</t>
+          <t>Series XS1704-A: Digitized from Cronin (2001) Table 1, column 'Total value', 1972-1995 (24 observations). Original table title: 'NZSNA in classical categories ($m)', Review of Political Economy 13(3), p. 11 (Table 1). Source CSV: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2001_Cronin_New_Zealand/tables.csv. Units: millions NZD, current prices.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; tables.csv</t>
+          <t>Cronin_2001, Table 1; tables.csv rows 2-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TV rose from NZD 10,423m in 1972 to NZD 123,284m in 1995, an increase of 1,083% in nominal terms. Gross output rose faster (1,196% over the same period, from 12,469m to 161,646m), reflecting the expansion of unproductive activity. The gap between gross output and total value widened notably from the late 1980s, as the financial sector and other unproductive industries grew rapidly following Rogernomics deregulation. The near-stagnation of TV in 1990-1992 (100,038 to 100,125) reflects real productive sector weakness during the post-reform recession, while gross output continued rising.</t>
+          <t>Annual total value (millions NZD, current prices): 1972=10423, 1973=12267, 1974=14233, 1975=15553, 1976=18847, 1977=23454, 1978=25195, 1979=28131, 1980=33317, 1981=38400, 1982=46691, 1983=52322, 1984=57628, 1985=67193, 1986=77232, 1987=87537, 1988=93389, 1989=96845, 1990=100038, 1991=100112, 1992=100125, 1993=105252, 1994=115853, 1995=123284.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, Table 1; tables.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>components</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TV components for terminal years from Table 1: 1972 — c=5,094m, v=1,739m, s=3,589m, TV=10,423m. 1995 — c=60,887m, v=15,347m, s=47,049m, TV=123,284m. Growth rates 1972-1995: c +1,095%, v +783%, s +1,211%, TV +1,083%. Surplus-value grew fastest, reflecting the rising rate of exploitation. Variable capital grew slowest, consistent with the rising rate of surplus-value (s/v from 206% to 307%).</t>
+          <t>TV rose from NZD 10,423m in 1972 to NZD 123,284m in 1995, an increase of 1,083% in nominal terms. Gross output rose faster (1,196% over the same period, from 12,469m to 161,646m), reflecting the expansion of unproductive activity. The gap between gross output and total value widened notably from the late 1980s, as the financial sector and other unproductive industries grew rapidly following Rogernomics deregulation. The near-stagnation of TV in 1990-1992 (100,038 to 100,125) reflects real productive sector weakness during the post-reform recession, while gross output continued rising.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 1; SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>unproductive_activity</t>
+          <t>components</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The divergence between gross output (neoclassical) and total value (classical) is the key empirical indicator of unproductive activity growth. In 1972 TV was 83.6% of gross output (10,423 / 12,469). By 1995 TV was 76.3% of gross output (123,284 / 161,646). This widening gap quantifies the increasing share of the economy devoted to classically unproductive activities — financial services, wholesale/retail trade beyond production-serving functions, government administration — that appear in GDP and gross output but not in classical total value.</t>
+          <t>TV components for terminal years from Table 1: 1972 — c=5,094m, v=1,739m, s=3,589m, TV=10,423m. 1995 — c=60,887m, v=15,347m, s=47,049m, TV=123,284m. Growth rates 1972-1995: c +1,095%, v +783%, s +1,211%, TV +1,083%. Surplus-value grew fastest, reflecting the rising rate of exploitation. Variable capital grew slowest, consistent with the rising rate of surplus-value (s/v from 206% to 307%).</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, Table 1; SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>unproductive_activity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cronin Fig 13: plots gross output vs total value 1972-1995, showing the divergence particularly from the late 1980s as unproductive activity expanded. Fig 14: compares GDP growth with classical value-added (v + s) growth, showing these do not consistently diverge — the divergence is at the gross output/total value level, not the net value-added level.</t>
+          <t>The divergence between gross output (neoclassical) and total value (classical) is the key empirical indicator of unproductive activity growth. In 1972 TV was 83.6% of gross output (10,423 / 12,469). By 1995 TV was 76.3% of gross output (123,284 / 161,646). This widening gap quantifies the increasing share of the economy devoted to classically unproductive activities — financial services, wholesale/retail trade beyond production-serving functions, government administration — that appear in GDP and gross output but not in classical total value.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5</t>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cronin Fig 13: plots gross output vs total value 1972-1995, showing the divergence particularly from the late 1980s as unproductive activity expanded. Fig 14: compares GDP growth with classical value-added (v + s) growth, showing these do not consistently diverge — the divergence is at the gross output/total value level, not the net value-added level.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>price_note</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>All TV values are in current prices (nominal NZD millions). No deflator is applied in Cronin's presentation; the classical framework treats value flows at current prices. Comparisons across time should account for NZ inflation, which was substantial over the 1972-1995 period (particularly the high-inflation 1970s-1980s).</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Cronin_2001, Table 1 header</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Total value in millions NZD directly digitized from Cronin (2001) Table 1. Classical concept excluding unproductive sectors; derived from NZSNA mapped to classical categories for 25 NZ production groups, 1972-1995. Current prices. No extension beyond 1995.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1376,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nominal (current price) series only; no real deflated version available from Cronin</t>
+          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1384,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NZSNA adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254, 269-270) introduce some estimation uncertainty</t>
+          <t>Nominal (current price) series only; no real deflated version available from Cronin</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1392,23 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>NZSNA adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254, 269-270) introduce some estimation uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Non-capitalist production assumed negligible — Cronin notes this introduces a small upward bias in TV</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>XS1701</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1416,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XS1702</t>
+          <t>XS1701</t>
         </is>
       </c>
     </row>
@@ -1415,37 +1424,45 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
+          <t>XS1702</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>XS1703</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cronin_2001</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Cronin_2001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1466,7 +1483,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1546,7 +1563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1972": 10423, "1995": 123284}</t>
+          <t>{"1972": 10423, "1984": 57628, "1989": 96845, "1995": 123284}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1704.xlsx
+++ b/extenbooks/XS1704.xlsx
@@ -954,7 +954,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1704_nz_total_value_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1704_nz_total_value_cronin2001.py`.</t>
+          <t>`data/source/external_studies/Cronin2001_cronin_table1_nzsna_classical_1972_1995.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1704_nz_total_value_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1704_nz_total_value_cronin2001.py`.</t>
         </is>
       </c>
     </row>
